--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64BA985-04EE-49A4-8D14-E46FAE0A8E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E301D553-168C-4BC5-A744-80A867622E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gathering" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Gathering!$B$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Gathering!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -164,15 +164,9 @@
     <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
   </si>
   <si>
-    <t>2024-05-14 22:00:00</t>
-  </si>
-  <si>
     <t>2024-04-19 22:00:00</t>
   </si>
   <si>
-    <t>2024-05-19 10:00:00</t>
-  </si>
-  <si>
     <t>2024-05-06 10:00:00</t>
   </si>
   <si>
@@ -256,12 +250,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2024-05-16 22:00:00</t>
-  </si>
-  <si>
-    <t>2024-05-23 10:00:00</t>
-  </si>
-  <si>
     <t>活動地點</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -450,6 +438,353 @@
   </si>
   <si>
     <t>FOOD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新年交流派對</t>
+  </si>
+  <si>
+    <t>輕鬆聊天迎接新的一年，無主題限制。</t>
+  </si>
+  <si>
+    <t>2026-01-10 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:59:00</t>
+  </si>
+  <si>
+    <t>2025-12-01 10:00:00</t>
+  </si>
+  <si>
+    <t>音樂分享夜</t>
+  </si>
+  <si>
+    <t>各自帶一首最近喜歡的歌來分享。</t>
+  </si>
+  <si>
+    <t>UPCOMING</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>2026-02-06 19:30:00</t>
+  </si>
+  <si>
+    <t>2026-02-03 23:59:00</t>
+  </si>
+  <si>
+    <t>基礎攝影學習</t>
+  </si>
+  <si>
+    <t>介紹基本構圖概念與實拍練習。</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:59:00</t>
+  </si>
+  <si>
+    <t>春季展覽同行</t>
+  </si>
+  <si>
+    <t>一起看當期藝術展，自由參觀。</t>
+  </si>
+  <si>
+    <t>2026-03-30 23:59:00</t>
+  </si>
+  <si>
+    <t>週末輕旅行</t>
+  </si>
+  <si>
+    <t>一日小旅行，行程不趕。</t>
+  </si>
+  <si>
+    <t>2026-04-18 23:59:00</t>
+  </si>
+  <si>
+    <t>慢跑入門團</t>
+  </si>
+  <si>
+    <t>適合初學者的慢速跑步活動。</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
+  </si>
+  <si>
+    <t>2026-05-13 23:59:00</t>
+  </si>
+  <si>
+    <t>桌遊同樂會</t>
+  </si>
+  <si>
+    <t>以輕策略與派對遊戲為主。</t>
+  </si>
+  <si>
+    <t>GAME</t>
+  </si>
+  <si>
+    <t>2026-06-03 23:59:00</t>
+  </si>
+  <si>
+    <t>美食探店團</t>
+  </si>
+  <si>
+    <t>嘗試新開的餐廳並交流心得。</t>
+  </si>
+  <si>
+    <t>2026-07-08 23:59:00</t>
+  </si>
+  <si>
+    <t>夏日晚間派對</t>
+  </si>
+  <si>
+    <t>簡單音樂與聊天，不吵鬧。</t>
+  </si>
+  <si>
+    <t>2026-07-28 23:59:00</t>
+  </si>
+  <si>
+    <t>歌單交換聚</t>
+  </si>
+  <si>
+    <t>分享彼此的私藏歌單。</t>
+  </si>
+  <si>
+    <t>2026-08-31 23:59:00</t>
+  </si>
+  <si>
+    <t>時間管理學習會</t>
+  </si>
+  <si>
+    <t>分享實用的時間規劃方法。</t>
+  </si>
+  <si>
+    <t>2026-10-06 23:59:00</t>
+  </si>
+  <si>
+    <t>秋季主題展覽</t>
+  </si>
+  <si>
+    <t>參觀設計主題展並交流看法。</t>
+  </si>
+  <si>
+    <t>2026-11-10 23:59:00</t>
+  </si>
+  <si>
+    <t>年度回顧小旅行</t>
+  </si>
+  <si>
+    <t>回顧一年生活的小型旅行。</t>
+  </si>
+  <si>
+    <t>2026-12-12 23:59:00</t>
+  </si>
+  <si>
+    <t>新年運動計畫</t>
+  </si>
+  <si>
+    <t>一起設定 2027 的運動目標。</t>
+  </si>
+  <si>
+    <t>2027-01-08 10:00:00</t>
+  </si>
+  <si>
+    <t>2027-01-05 23:59:00</t>
+  </si>
+  <si>
+    <t>派對遊戲之夜</t>
+  </si>
+  <si>
+    <t>派對型桌遊為主，輕鬆玩。</t>
+  </si>
+  <si>
+    <t>2027-02-05 19:30:00</t>
+  </si>
+  <si>
+    <t>2027-02-02 23:59:00</t>
+  </si>
+  <si>
+    <t>美食分享聚餐</t>
+  </si>
+  <si>
+    <t>每個人推薦一道喜歡的料理。</t>
+  </si>
+  <si>
+    <t>2027-03-06 18:30:00</t>
+  </si>
+  <si>
+    <t>2027-03-03 23:59:00</t>
+  </si>
+  <si>
+    <t>主題交流聚會</t>
+  </si>
+  <si>
+    <t>不限主題，自由聊天交流。</t>
+  </si>
+  <si>
+    <t>2027-04-09 14:00:00</t>
+  </si>
+  <si>
+    <t>2027-04-06 23:59:00</t>
+  </si>
+  <si>
+    <t>學習成果分享</t>
+  </si>
+  <si>
+    <t>分享近期學到的新技能。</t>
+  </si>
+  <si>
+    <t>2027-05-15 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-05-12 23:59:00</t>
+  </si>
+  <si>
+    <t>春季小派對</t>
+  </si>
+  <si>
+    <t>簡單聚會，輕音樂聊天。</t>
+  </si>
+  <si>
+    <t>2027-06-04 18:00:00</t>
+  </si>
+  <si>
+    <t>2027-06-01 23:59:00</t>
+  </si>
+  <si>
+    <t>年度自由聚會</t>
+  </si>
+  <si>
+    <t>沒有特定主題的聚會。</t>
+  </si>
+  <si>
+    <t>2027-07-23 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-20 23:59:00</t>
+  </si>
+  <si>
+    <t>2025-12-15 9:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-14 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-04-02 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-24 8:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-16 7:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-06 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-11 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-01 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-09 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-11-14 11:00:00</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>2026-12-18 9:00:00</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2025-12-24 11:38:27</t>
+  </si>
+  <si>
+    <t>2025-12-24 11:38:27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 3 樓（共享空間 A）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市樂音街 45 號 1 樓（音樂咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 2 樓 201 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市藝文路 160 號（美術館）</t>
+  </si>
+  <si>
+    <t>星辰縣海灣小鎮濱海路 12 號</t>
+  </si>
+  <si>
+    <t>星辰縣河濱鎮河岸路 300 號（河濱公園）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市棋樂街 27 號（桌遊店）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市饗宴路 99 號（美食街）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市天際路 180 號 頂樓（屋頂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市旋律路 52 號 2 樓（音樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星航路 10 號 4 樓（會議室 B）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市展星路 200 號（展覽中心）</t>
+  </si>
+  <si>
+    <t>星辰縣山城市雲嶺路 66 號</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市動能路 155 號（運動中心）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市歡聚路 78 號 3 樓（娛樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市微醺街 33 號（餐酒館）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市晨星路 18 號（咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 3 樓 305 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 5 樓（共享空間 C）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市聚光路 140 號（活動空間）</t>
+  </si>
+  <si>
+    <t>2025-12-16 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-14 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-23 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-19 10:00:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +795,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,13 +1199,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P159"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -881,16 +1216,16 @@
         <v>10</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>15</v>
@@ -899,7 +1234,7 @@
         <v>16</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>18</v>
@@ -914,7 +1249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -928,13 +1263,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>4</v>
@@ -943,7 +1278,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>5</v>
@@ -957,247 +1292,249 @@
       <c r="N2" s="14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F3" s="2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F4" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2">
-        <v>200</v>
+        <v>5400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
       </c>
       <c r="G5" s="2">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="11" customFormat="1">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>60</v>
       </c>
       <c r="F7" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2">
-        <v>5400</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>61</v>
@@ -1206,33 +1543,31 @@
         <v>30</v>
       </c>
       <c r="G8" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1246,7 +1581,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2">
         <v>15</v>
@@ -1255,43 +1590,44 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" s="11" customFormat="1">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1300,30 +1636,29 @@
         <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1331,91 +1666,91 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2">
         <v>200</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2">
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>116</v>
+        <v>231</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1423,613 +1758,1247 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2">
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="F14" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G14" s="2">
-        <v>35000</v>
+        <v>300</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="11" customFormat="1">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>123</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="F15" s="2">
-        <v>300</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>81</v>
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <v>200</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="L15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>129</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="F16" s="2">
-        <v>3000</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
+      </c>
+      <c r="G16" s="2">
+        <v>800</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="6"/>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="2">
+        <v>40</v>
+      </c>
+      <c r="G17" s="2">
+        <v>35000</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-      <c r="G18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="6"/>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>24</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="2">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2">
+        <v>500</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="6"/>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F19" s="2">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1200</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="6"/>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>38</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F20" s="2">
+        <v>20</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="6"/>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>40</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="2">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="4"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="6"/>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F22" s="2">
+        <v>12</v>
+      </c>
+      <c r="G22" s="2">
+        <v>150</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="4"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="6"/>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
+        <v>600</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="4"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="6"/>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>21</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" s="2">
+        <v>28</v>
+      </c>
+      <c r="G24" s="2">
+        <v>400</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="4"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="6"/>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F25" s="2">
+        <v>14</v>
+      </c>
+      <c r="G25" s="2">
+        <v>250</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="4"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="6"/>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>30</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F26" s="2">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="4"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="6"/>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="2">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2">
+        <v>450</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="4"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="6"/>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>35</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="2">
+        <v>16</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="4"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="6"/>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="4"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="6"/>
+    <row r="30" spans="1:16">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="2">
+        <v>18</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="4"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="6"/>
+    <row r="31" spans="1:16">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>26</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F31" s="2">
+        <v>16</v>
+      </c>
+      <c r="G31" s="2">
+        <v>200</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="4"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="6"/>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>4</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F32" s="2">
+        <v>12</v>
+      </c>
+      <c r="G32" s="2">
+        <v>800</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="4"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="6"/>
+    <row r="33" spans="1:16">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2">
+        <v>200</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="4"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="6"/>
+    <row r="34" spans="1:16">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>13</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F34" s="2">
+        <v>20</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="4"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="6"/>
+    <row r="35" spans="1:16">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>33</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F35" s="2">
+        <v>24</v>
+      </c>
+      <c r="G35" s="2">
+        <v>350</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="4"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="6"/>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>8</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F36" s="2">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" s="2"/>
-      <c r="B37" s="4"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="7"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="L37" s="2"/>
       <c r="M37" s="3"/>
-      <c r="N37" s="6"/>
+      <c r="N37" s="3"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" s="2"/>
-      <c r="B38" s="4"/>
+      <c r="B38" s="2"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="2"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="7"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
+      <c r="L38" s="2"/>
       <c r="M38" s="3"/>
-      <c r="N38" s="6"/>
+      <c r="N38" s="3"/>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" s="2"/>
-      <c r="B39" s="4"/>
+      <c r="B39" s="2"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="2"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="7"/>
+      <c r="I39" s="2"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+      <c r="L39" s="2"/>
       <c r="M39" s="3"/>
-      <c r="N39" s="6"/>
+      <c r="N39" s="3"/>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" s="2"/>
-      <c r="B40" s="4"/>
+      <c r="B40" s="2"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="2"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="7"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
+      <c r="L40" s="2"/>
       <c r="M40" s="3"/>
-      <c r="N40" s="6"/>
+      <c r="N40" s="3"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" s="2"/>
-      <c r="B41" s="4"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="2"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="7"/>
+      <c r="I41" s="2"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="L41" s="2"/>
       <c r="M41" s="3"/>
-      <c r="N41" s="6"/>
+      <c r="N41" s="3"/>
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" s="2"/>
-      <c r="B42" s="4"/>
+      <c r="B42" s="2"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="2"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="7"/>
+      <c r="I42" s="2"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="L42" s="2"/>
       <c r="M42" s="3"/>
-      <c r="N42" s="6"/>
+      <c r="N42" s="3"/>
       <c r="O42" s="6"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" s="2"/>
-      <c r="B43" s="4"/>
+      <c r="B43" s="2"/>
       <c r="C43" s="4"/>
       <c r="D43" s="2"/>
       <c r="E43" s="4"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="7"/>
+      <c r="I43" s="2"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="L43" s="2"/>
       <c r="M43" s="3"/>
-      <c r="N43" s="6"/>
+      <c r="N43" s="3"/>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
+      <c r="B44" s="2"/>
       <c r="C44" s="4"/>
       <c r="D44" s="2"/>
       <c r="E44" s="4"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="7"/>
+      <c r="I44" s="2"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="L44" s="2"/>
       <c r="M44" s="3"/>
-      <c r="N44" s="6"/>
+      <c r="N44" s="3"/>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="A45" s="2"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2047,7 +3016,7 @@
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="A46" s="2"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2065,7 +3034,7 @@
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16">
       <c r="A47" s="2"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2083,7 +3052,7 @@
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
       <c r="A48" s="2"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2101,7 +3070,7 @@
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2119,7 +3088,7 @@
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2137,7 +3106,7 @@
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2155,7 +3124,7 @@
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2173,7 +3142,7 @@
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16">
       <c r="A53" s="2"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2191,7 +3160,7 @@
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16">
       <c r="A54" s="2"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2209,7 +3178,7 @@
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16">
       <c r="A55" s="2"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2227,7 +3196,7 @@
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16">
       <c r="A56" s="2"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2245,7 +3214,7 @@
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16">
       <c r="A57" s="2"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2263,7 +3232,7 @@
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16">
       <c r="A58" s="2"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2281,7 +3250,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2299,7 +3268,7 @@
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16">
       <c r="A60" s="2"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2317,7 +3286,7 @@
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16">
       <c r="A61" s="2"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2335,7 +3304,7 @@
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16">
       <c r="A62" s="2"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2353,7 +3322,7 @@
       <c r="O62" s="6"/>
       <c r="P62" s="6"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16">
       <c r="A63" s="2"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2371,7 +3340,7 @@
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16">
       <c r="A64" s="2"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2389,7 +3358,7 @@
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16">
       <c r="A65" s="2"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2407,7 +3376,7 @@
       <c r="O65" s="6"/>
       <c r="P65" s="6"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16">
       <c r="A66" s="2"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2425,7 +3394,7 @@
       <c r="O66" s="6"/>
       <c r="P66" s="6"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16">
       <c r="A67" s="2"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2443,7 +3412,7 @@
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16">
       <c r="A68" s="2"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2461,7 +3430,7 @@
       <c r="O68" s="6"/>
       <c r="P68" s="6"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16">
       <c r="A69" s="2"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2479,7 +3448,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16">
       <c r="A70" s="2"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2497,7 +3466,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16">
       <c r="A71" s="2"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2515,7 +3484,7 @@
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16">
       <c r="A72" s="2"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2533,7 +3502,7 @@
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16">
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2551,7 +3520,7 @@
       <c r="O73" s="6"/>
       <c r="P73" s="6"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16">
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2569,7 +3538,7 @@
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16">
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2587,7 +3556,7 @@
       <c r="O75" s="6"/>
       <c r="P75" s="6"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16">
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2605,7 +3574,7 @@
       <c r="O76" s="6"/>
       <c r="P76" s="6"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16">
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2623,7 +3592,7 @@
       <c r="O77" s="6"/>
       <c r="P77" s="6"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16">
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2641,7 +3610,7 @@
       <c r="O78" s="6"/>
       <c r="P78" s="6"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16">
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2659,7 +3628,7 @@
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16">
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2677,7 +3646,7 @@
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16">
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2695,7 +3664,7 @@
       <c r="O81" s="6"/>
       <c r="P81" s="6"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16">
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2713,7 +3682,7 @@
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16">
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2731,7 +3700,7 @@
       <c r="O83" s="6"/>
       <c r="P83" s="6"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16">
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2749,7 +3718,7 @@
       <c r="O84" s="6"/>
       <c r="P84" s="6"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16">
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2767,7 +3736,7 @@
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16">
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2785,7 +3754,7 @@
       <c r="O86" s="6"/>
       <c r="P86" s="6"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16">
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2803,7 +3772,7 @@
       <c r="O87" s="6"/>
       <c r="P87" s="6"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16">
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2821,7 +3790,7 @@
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16">
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2839,7 +3808,7 @@
       <c r="O89" s="6"/>
       <c r="P89" s="6"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2857,7 +3826,7 @@
       <c r="O90" s="6"/>
       <c r="P90" s="6"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16">
       <c r="A91" s="2"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2875,7 +3844,7 @@
       <c r="O91" s="6"/>
       <c r="P91" s="6"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16">
       <c r="A92" s="2"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2893,7 +3862,7 @@
       <c r="O92" s="6"/>
       <c r="P92" s="6"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16">
       <c r="A93" s="2"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2911,7 +3880,7 @@
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16">
       <c r="A94" s="2"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2929,7 +3898,7 @@
       <c r="O94" s="6"/>
       <c r="P94" s="6"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16">
       <c r="A95" s="2"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -2947,7 +3916,7 @@
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16">
       <c r="A96" s="2"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2965,7 +3934,7 @@
       <c r="O96" s="6"/>
       <c r="P96" s="6"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16">
       <c r="A97" s="2"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -2983,7 +3952,7 @@
       <c r="O97" s="6"/>
       <c r="P97" s="6"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16">
       <c r="A98" s="2"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2998,7 +3967,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16">
       <c r="A99" s="2"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3013,7 +3982,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16">
       <c r="A100" s="2"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3028,7 +3997,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16">
       <c r="A101" s="2"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3043,7 +4012,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16">
       <c r="A102" s="2"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3058,7 +4027,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3073,7 +4042,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3088,7 +4057,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3103,7 +4072,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3118,7 +4087,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3133,7 +4102,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3148,7 +4117,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3163,7 +4132,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3178,7 +4147,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16">
       <c r="A111" s="2"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3193,7 +4162,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16">
       <c r="A112" s="2"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3208,7 +4177,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13">
       <c r="A113" s="2"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3223,7 +4192,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13">
       <c r="A114" s="2"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3238,7 +4207,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13">
       <c r="A115" s="2"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3253,7 +4222,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13">
       <c r="A116" s="2"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3268,7 +4237,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13">
       <c r="A117" s="2"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3283,7 +4252,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13">
       <c r="A118" s="2"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3298,7 +4267,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13">
       <c r="A119" s="2"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3313,7 +4282,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13">
       <c r="A120" s="2"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3328,7 +4297,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13">
       <c r="A121" s="2"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3343,7 +4312,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13">
       <c r="A122" s="2"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3358,7 +4327,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13">
       <c r="A123" s="2"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3373,7 +4342,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13">
       <c r="A124" s="2"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3388,7 +4357,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13">
       <c r="A125" s="2"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3403,7 +4372,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13">
       <c r="A126" s="2"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3418,7 +4387,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13">
       <c r="A127" s="2"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3433,7 +4402,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13">
       <c r="A128" s="2"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3448,7 +4417,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13">
       <c r="A129" s="2"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3463,7 +4432,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13">
       <c r="A130" s="2"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3478,7 +4447,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13">
       <c r="A131" s="2"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3493,7 +4462,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13">
       <c r="A132" s="2"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -3508,7 +4477,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13">
       <c r="A133" s="2"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -3523,7 +4492,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13">
       <c r="A134" s="2"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -3538,7 +4507,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13">
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
@@ -3547,7 +4516,7 @@
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13">
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
@@ -3556,7 +4525,7 @@
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13">
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
@@ -3565,7 +4534,7 @@
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13">
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
@@ -3574,7 +4543,7 @@
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13">
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
@@ -3583,7 +4552,7 @@
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13">
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
@@ -3592,7 +4561,7 @@
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13">
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
@@ -3601,7 +4570,7 @@
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13">
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
@@ -3610,7 +4579,7 @@
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13">
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -3619,7 +4588,7 @@
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13">
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
@@ -3628,77 +4597,77 @@
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
-    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="10:12">
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
     </row>
-    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="10:12">
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="10:12">
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="10:12">
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="10:12">
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="10:12">
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="10:12">
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="10:12">
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="10:12">
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="10:12">
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="10:12">
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="10:12">
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="10:12">
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="10:12">
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="10:12">
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>

--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E301D553-168C-4BC5-A744-80A867622E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74DD1E-6DC1-4C05-BAE2-2D4DADD3407E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22830" yWindow="3750" windowWidth="18585" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gathering" sheetId="1" r:id="rId1"/>
@@ -45,746 +45,748 @@
     <t>status</t>
   </si>
   <si>
+    <t>isArchived</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>updatedAt</t>
+  </si>
+  <si>
+    <t>擁有者 id</t>
+  </si>
+  <si>
+    <t>標題</t>
+  </si>
+  <si>
+    <t>創建日期</t>
+  </si>
+  <si>
+    <t>最後更新日期</t>
+  </si>
+  <si>
+    <t>封存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主鍵 id</t>
+  </si>
+  <si>
+    <t>結束狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚會分類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名截止日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要不要來學AI</t>
+  </si>
+  <si>
+    <t>很怕報名的人都跑了所以先說：前面會有吃的，然後才是講座。一起坐一起滑手機也可以。</t>
+  </si>
+  <si>
+    <t>北海道泡湯團</t>
+  </si>
+  <si>
+    <t>純粹想泡湯，有人要跟嗎？白天行程我應該會亂走一通。</t>
+  </si>
+  <si>
+    <t>攝影展揪一波</t>
+  </si>
+  <si>
+    <t>主揪可能只會拍人，不一定在看展，想來亂晃的可以+1。</t>
+  </si>
+  <si>
+    <t>啤酒節生死鬥</t>
+  </si>
+  <si>
+    <t>去年被灌到回不了家，今年打算吃東西為主，誰要來幫顧戰力。</t>
+  </si>
+  <si>
+    <t>花蓮旅遊但會累爆</t>
+  </si>
+  <si>
+    <t>有點後悔自己排這麼滿的行程，但錢都繳了只能硬著頭皮揪人了。</t>
+  </si>
+  <si>
+    <t>部門耶誕交換禮物</t>
+  </si>
+  <si>
+    <t>我們部門自己辦的，可以帶朋友來！但先說活動很吵XD</t>
+  </si>
+  <si>
+    <t>吃吃找找行軍賽</t>
+  </si>
+  <si>
+    <t>這不是什麼正經活動，單純揪大家一起吃+迷路，怕吵勿報。</t>
+  </si>
+  <si>
+    <t>學習營但中間有在偷玩</t>
+  </si>
+  <si>
+    <t>中間會有偷懶時段可以聊天，要認真學的人也歡迎，但我可能會滑手機。</t>
+  </si>
+  <si>
+    <t>週末沒事來跳舞？</t>
+  </si>
+  <si>
+    <t>音樂很大聲，但來了應該會很開心，穿輕鬆一點不要尷尬～</t>
+  </si>
+  <si>
+    <t>開發者社群小小揪</t>
+  </si>
+  <si>
+    <t>沒有很專業，真的就只是想找人一起講幹話，討論技術也可以。</t>
+  </si>
+  <si>
+    <t>手作體驗</t>
+  </si>
+  <si>
+    <t>聚集志同道合的人，共度特別時光的手作體驗。</t>
+  </si>
+  <si>
+    <t>AI 開發者社群聚會</t>
+  </si>
+  <si>
+    <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
+  </si>
+  <si>
+    <t>2024-04-19 22:00:00</t>
+  </si>
+  <si>
+    <t>2024-05-06 10:00:00</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>PARTY</t>
+  </si>
+  <si>
+    <t>LEARNING</t>
+  </si>
+  <si>
+    <t>TRAVEL</t>
+  </si>
+  <si>
+    <t>EXHIBITION</t>
+  </si>
+  <si>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>日本北海道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸福縣快樂市陽光路 220 號</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市流星大道 88 號</t>
+  </si>
+  <si>
+    <t>彩虹縣晴夢市繽紛街 12 巷 6 號</t>
+  </si>
+  <si>
+    <t>幻月縣霜影市月華路 377 號</t>
+  </si>
+  <si>
+    <t>青風縣翡翠市清泉街 5 巷 19 號</t>
+  </si>
+  <si>
+    <t>琉璃縣光海市瑠光路 102 號</t>
+  </si>
+  <si>
+    <t>雲岫縣晴嶺市雲端大道 511 號</t>
+  </si>
+  <si>
+    <t>長樂縣安寧市和風街 33 巷 2 弄 10 號</t>
+  </si>
+  <si>
+    <t>星語縣夢境市星光一路 72 號</t>
+  </si>
+  <si>
+    <t>霧森縣翠柏市林語街 4 巷 28 號</t>
+  </si>
+  <si>
+    <t>晨光縣朝陽市朝日路 260 號</t>
+  </si>
+  <si>
+    <t>活動費用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加人數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動地點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participantNumbers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>達悟族之美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參觀達悟族的鐵桶和丁字褲文化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台東縣蘭嶼鄉</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-03 10:34:28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-06-01 07:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-05-25 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起去安大林森公園哭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安大林森公園</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-31 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-12-26 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-03 10:40:13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-01 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-05 14:30:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-09 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-19 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-16 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-06 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-24 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-12 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-15 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-22 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-11 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-12 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-29 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-08 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-11 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-19 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-08 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-09 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-26 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-08 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-04 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-28 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-01 13:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-11 05:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-16 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOOD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新年交流派對</t>
+  </si>
+  <si>
+    <t>輕鬆聊天迎接新的一年，無主題限制。</t>
+  </si>
+  <si>
+    <t>2026-01-10 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:59:00</t>
+  </si>
+  <si>
+    <t>2025-12-01 10:00:00</t>
+  </si>
+  <si>
+    <t>音樂分享夜</t>
+  </si>
+  <si>
+    <t>各自帶一首最近喜歡的歌來分享。</t>
+  </si>
+  <si>
+    <t>UPCOMING</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>2026-02-06 19:30:00</t>
+  </si>
+  <si>
+    <t>2026-02-03 23:59:00</t>
+  </si>
+  <si>
+    <t>基礎攝影學習</t>
+  </si>
+  <si>
+    <t>介紹基本構圖概念與實拍練習。</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:59:00</t>
+  </si>
+  <si>
+    <t>春季展覽同行</t>
+  </si>
+  <si>
+    <t>一起看當期藝術展，自由參觀。</t>
+  </si>
+  <si>
+    <t>2026-03-30 23:59:00</t>
+  </si>
+  <si>
+    <t>週末輕旅行</t>
+  </si>
+  <si>
+    <t>一日小旅行，行程不趕。</t>
+  </si>
+  <si>
+    <t>2026-04-18 23:59:00</t>
+  </si>
+  <si>
+    <t>慢跑入門團</t>
+  </si>
+  <si>
+    <t>適合初學者的慢速跑步活動。</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
+  </si>
+  <si>
+    <t>2026-05-13 23:59:00</t>
+  </si>
+  <si>
+    <t>桌遊同樂會</t>
+  </si>
+  <si>
+    <t>以輕策略與派對遊戲為主。</t>
+  </si>
+  <si>
+    <t>GAME</t>
+  </si>
+  <si>
+    <t>2026-06-03 23:59:00</t>
+  </si>
+  <si>
+    <t>美食探店團</t>
+  </si>
+  <si>
+    <t>嘗試新開的餐廳並交流心得。</t>
+  </si>
+  <si>
+    <t>2026-07-08 23:59:00</t>
+  </si>
+  <si>
+    <t>夏日晚間派對</t>
+  </si>
+  <si>
+    <t>簡單音樂與聊天，不吵鬧。</t>
+  </si>
+  <si>
+    <t>2026-07-28 23:59:00</t>
+  </si>
+  <si>
+    <t>歌單交換聚</t>
+  </si>
+  <si>
+    <t>分享彼此的私藏歌單。</t>
+  </si>
+  <si>
+    <t>2026-08-31 23:59:00</t>
+  </si>
+  <si>
+    <t>時間管理學習會</t>
+  </si>
+  <si>
+    <t>分享實用的時間規劃方法。</t>
+  </si>
+  <si>
+    <t>2026-10-06 23:59:00</t>
+  </si>
+  <si>
+    <t>秋季主題展覽</t>
+  </si>
+  <si>
+    <t>參觀設計主題展並交流看法。</t>
+  </si>
+  <si>
+    <t>2026-11-10 23:59:00</t>
+  </si>
+  <si>
+    <t>年度回顧小旅行</t>
+  </si>
+  <si>
+    <t>回顧一年生活的小型旅行。</t>
+  </si>
+  <si>
+    <t>2026-12-12 23:59:00</t>
+  </si>
+  <si>
+    <t>新年運動計畫</t>
+  </si>
+  <si>
+    <t>一起設定 2027 的運動目標。</t>
+  </si>
+  <si>
+    <t>2027-01-08 10:00:00</t>
+  </si>
+  <si>
+    <t>2027-01-05 23:59:00</t>
+  </si>
+  <si>
+    <t>派對遊戲之夜</t>
+  </si>
+  <si>
+    <t>派對型桌遊為主，輕鬆玩。</t>
+  </si>
+  <si>
+    <t>2027-02-05 19:30:00</t>
+  </si>
+  <si>
+    <t>2027-02-02 23:59:00</t>
+  </si>
+  <si>
+    <t>美食分享聚餐</t>
+  </si>
+  <si>
+    <t>每個人推薦一道喜歡的料理。</t>
+  </si>
+  <si>
+    <t>2027-03-06 18:30:00</t>
+  </si>
+  <si>
+    <t>2027-03-03 23:59:00</t>
+  </si>
+  <si>
+    <t>主題交流聚會</t>
+  </si>
+  <si>
+    <t>不限主題，自由聊天交流。</t>
+  </si>
+  <si>
+    <t>2027-04-09 14:00:00</t>
+  </si>
+  <si>
+    <t>2027-04-06 23:59:00</t>
+  </si>
+  <si>
+    <t>學習成果分享</t>
+  </si>
+  <si>
+    <t>分享近期學到的新技能。</t>
+  </si>
+  <si>
+    <t>2027-05-15 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-05-12 23:59:00</t>
+  </si>
+  <si>
+    <t>春季小派對</t>
+  </si>
+  <si>
+    <t>簡單聚會，輕音樂聊天。</t>
+  </si>
+  <si>
+    <t>2027-06-04 18:00:00</t>
+  </si>
+  <si>
+    <t>2027-06-01 23:59:00</t>
+  </si>
+  <si>
+    <t>年度自由聚會</t>
+  </si>
+  <si>
+    <t>沒有特定主題的聚會。</t>
+  </si>
+  <si>
+    <t>2027-07-23 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-20 23:59:00</t>
+  </si>
+  <si>
+    <t>2025-12-15 9:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-14 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-04-02 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-24 8:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-16 7:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-06 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-11 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-01 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-09 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-11-14 11:00:00</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>2026-12-18 9:00:00</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2025-12-24 11:38:27</t>
+  </si>
+  <si>
+    <t>2025-12-24 11:38:27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 3 樓（共享空間 A）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市樂音街 45 號 1 樓（音樂咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 2 樓 201 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市藝文路 160 號（美術館）</t>
+  </si>
+  <si>
+    <t>星辰縣海灣小鎮濱海路 12 號</t>
+  </si>
+  <si>
+    <t>星辰縣河濱鎮河岸路 300 號（河濱公園）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市棋樂街 27 號（桌遊店）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市饗宴路 99 號（美食街）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市天際路 180 號 頂樓（屋頂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市旋律路 52 號 2 樓（音樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星航路 10 號 4 樓（會議室 B）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市展星路 200 號（展覽中心）</t>
+  </si>
+  <si>
+    <t>星辰縣山城市雲嶺路 66 號</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市動能路 155 號（運動中心）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市歡聚路 78 號 3 樓（娛樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市微醺街 33 號（餐酒館）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市晨星路 18 號（咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 3 樓 305 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 5 樓（共享空間 C）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市聚光路 140 號（活動空間）</t>
+  </si>
+  <si>
+    <t>2025-12-16 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-14 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-23 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-19 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>dueDate</t>
-  </si>
-  <si>
-    <t>isArchived</t>
-  </si>
-  <si>
-    <t>createdAt</t>
-  </si>
-  <si>
-    <t>updatedAt</t>
-  </si>
-  <si>
-    <t>擁有者 id</t>
-  </si>
-  <si>
-    <t>標題</t>
-  </si>
-  <si>
-    <t>創建日期</t>
-  </si>
-  <si>
-    <t>最後更新日期</t>
-  </si>
-  <si>
-    <t>封存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主鍵 id</t>
-  </si>
-  <si>
-    <t>結束狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚會分類</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名截止日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要不要來學AI</t>
-  </si>
-  <si>
-    <t>很怕報名的人都跑了所以先說：前面會有吃的，然後才是講座。一起坐一起滑手機也可以。</t>
-  </si>
-  <si>
-    <t>北海道泡湯團</t>
-  </si>
-  <si>
-    <t>純粹想泡湯，有人要跟嗎？白天行程我應該會亂走一通。</t>
-  </si>
-  <si>
-    <t>攝影展揪一波</t>
-  </si>
-  <si>
-    <t>主揪可能只會拍人，不一定在看展，想來亂晃的可以+1。</t>
-  </si>
-  <si>
-    <t>啤酒節生死鬥</t>
-  </si>
-  <si>
-    <t>去年被灌到回不了家，今年打算吃東西為主，誰要來幫顧戰力。</t>
-  </si>
-  <si>
-    <t>花蓮旅遊但會累爆</t>
-  </si>
-  <si>
-    <t>有點後悔自己排這麼滿的行程，但錢都繳了只能硬著頭皮揪人了。</t>
-  </si>
-  <si>
-    <t>部門耶誕交換禮物</t>
-  </si>
-  <si>
-    <t>我們部門自己辦的，可以帶朋友來！但先說活動很吵XD</t>
-  </si>
-  <si>
-    <t>吃吃找找行軍賽</t>
-  </si>
-  <si>
-    <t>這不是什麼正經活動，單純揪大家一起吃+迷路，怕吵勿報。</t>
-  </si>
-  <si>
-    <t>學習營但中間有在偷玩</t>
-  </si>
-  <si>
-    <t>中間會有偷懶時段可以聊天，要認真學的人也歡迎，但我可能會滑手機。</t>
-  </si>
-  <si>
-    <t>週末沒事來跳舞？</t>
-  </si>
-  <si>
-    <t>音樂很大聲，但來了應該會很開心，穿輕鬆一點不要尷尬～</t>
-  </si>
-  <si>
-    <t>開發者社群小小揪</t>
-  </si>
-  <si>
-    <t>沒有很專業，真的就只是想找人一起講幹話，討論技術也可以。</t>
-  </si>
-  <si>
-    <t>手作體驗</t>
-  </si>
-  <si>
-    <t>聚集志同道合的人，共度特別時光的手作體驗。</t>
-  </si>
-  <si>
-    <t>AI 開發者社群聚會</t>
-  </si>
-  <si>
-    <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
-  </si>
-  <si>
-    <t>2024-04-19 22:00:00</t>
-  </si>
-  <si>
-    <t>2024-05-06 10:00:00</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>PARTY</t>
-  </si>
-  <si>
-    <t>LEARNING</t>
-  </si>
-  <si>
-    <t>TRAVEL</t>
-  </si>
-  <si>
-    <t>EXHIBITION</t>
-  </si>
-  <si>
-    <t>FOOD</t>
-  </si>
-  <si>
-    <t>OTHER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>活動描述</t>
-  </si>
-  <si>
-    <t>日本北海道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸福縣快樂市陽光路 220 號</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市流星大道 88 號</t>
-  </si>
-  <si>
-    <t>彩虹縣晴夢市繽紛街 12 巷 6 號</t>
-  </si>
-  <si>
-    <t>幻月縣霜影市月華路 377 號</t>
-  </si>
-  <si>
-    <t>青風縣翡翠市清泉街 5 巷 19 號</t>
-  </si>
-  <si>
-    <t>琉璃縣光海市瑠光路 102 號</t>
-  </si>
-  <si>
-    <t>雲岫縣晴嶺市雲端大道 511 號</t>
-  </si>
-  <si>
-    <t>長樂縣安寧市和風街 33 巷 2 弄 10 號</t>
-  </si>
-  <si>
-    <t>星語縣夢境市星光一路 72 號</t>
-  </si>
-  <si>
-    <t>霧森縣翠柏市林語街 4 巷 28 號</t>
-  </si>
-  <si>
-    <t>晨光縣朝陽市朝日路 260 號</t>
-  </si>
-  <si>
-    <t>活動費用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參加人數</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動地點</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>location</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>participantNumbers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>達悟族之美</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參觀達悟族的鐵桶和丁字褲文化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台東縣蘭嶼鄉</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-03 10:34:28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-06-01 07:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-05-25 23:59:59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一起去安大林森公園哭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一起分享今年的洗褲哀樂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安大林森公園</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-12-31 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-12-26 23:59:59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-03 10:40:13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-01 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-05 14:30:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-09 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-19 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-16 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-06 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-24 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-12 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-14 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-24 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-15 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-22 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-11 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-12 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-09 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-09 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-29 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-05-08 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-14 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-11 00:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-19 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-08 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-09 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-26 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-08 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-05-04 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-28 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-01 13:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-07-11 05:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-03-16 23:59:59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FOOD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新年交流派對</t>
-  </si>
-  <si>
-    <t>輕鬆聊天迎接新的一年，無主題限制。</t>
-  </si>
-  <si>
-    <t>2026-01-10 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 23:59:00</t>
-  </si>
-  <si>
-    <t>2025-12-01 10:00:00</t>
-  </si>
-  <si>
-    <t>音樂分享夜</t>
-  </si>
-  <si>
-    <t>各自帶一首最近喜歡的歌來分享。</t>
-  </si>
-  <si>
-    <t>UPCOMING</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>2026-02-06 19:30:00</t>
-  </si>
-  <si>
-    <t>2026-02-03 23:59:00</t>
-  </si>
-  <si>
-    <t>基礎攝影學習</t>
-  </si>
-  <si>
-    <t>介紹基本構圖概念與實拍練習。</t>
-  </si>
-  <si>
-    <t>2026-03-10 23:59:00</t>
-  </si>
-  <si>
-    <t>春季展覽同行</t>
-  </si>
-  <si>
-    <t>一起看當期藝術展，自由參觀。</t>
-  </si>
-  <si>
-    <t>2026-03-30 23:59:00</t>
-  </si>
-  <si>
-    <t>週末輕旅行</t>
-  </si>
-  <si>
-    <t>一日小旅行，行程不趕。</t>
-  </si>
-  <si>
-    <t>2026-04-18 23:59:00</t>
-  </si>
-  <si>
-    <t>慢跑入門團</t>
-  </si>
-  <si>
-    <t>適合初學者的慢速跑步活動。</t>
-  </si>
-  <si>
-    <t>SPORTS</t>
-  </si>
-  <si>
-    <t>2026-05-13 23:59:00</t>
-  </si>
-  <si>
-    <t>桌遊同樂會</t>
-  </si>
-  <si>
-    <t>以輕策略與派對遊戲為主。</t>
-  </si>
-  <si>
-    <t>GAME</t>
-  </si>
-  <si>
-    <t>2026-06-03 23:59:00</t>
-  </si>
-  <si>
-    <t>美食探店團</t>
-  </si>
-  <si>
-    <t>嘗試新開的餐廳並交流心得。</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:59:00</t>
-  </si>
-  <si>
-    <t>夏日晚間派對</t>
-  </si>
-  <si>
-    <t>簡單音樂與聊天，不吵鬧。</t>
-  </si>
-  <si>
-    <t>2026-07-28 23:59:00</t>
-  </si>
-  <si>
-    <t>歌單交換聚</t>
-  </si>
-  <si>
-    <t>分享彼此的私藏歌單。</t>
-  </si>
-  <si>
-    <t>2026-08-31 23:59:00</t>
-  </si>
-  <si>
-    <t>時間管理學習會</t>
-  </si>
-  <si>
-    <t>分享實用的時間規劃方法。</t>
-  </si>
-  <si>
-    <t>2026-10-06 23:59:00</t>
-  </si>
-  <si>
-    <t>秋季主題展覽</t>
-  </si>
-  <si>
-    <t>參觀設計主題展並交流看法。</t>
-  </si>
-  <si>
-    <t>2026-11-10 23:59:00</t>
-  </si>
-  <si>
-    <t>年度回顧小旅行</t>
-  </si>
-  <si>
-    <t>回顧一年生活的小型旅行。</t>
-  </si>
-  <si>
-    <t>2026-12-12 23:59:00</t>
-  </si>
-  <si>
-    <t>新年運動計畫</t>
-  </si>
-  <si>
-    <t>一起設定 2027 的運動目標。</t>
-  </si>
-  <si>
-    <t>2027-01-08 10:00:00</t>
-  </si>
-  <si>
-    <t>2027-01-05 23:59:00</t>
-  </si>
-  <si>
-    <t>派對遊戲之夜</t>
-  </si>
-  <si>
-    <t>派對型桌遊為主，輕鬆玩。</t>
-  </si>
-  <si>
-    <t>2027-02-05 19:30:00</t>
-  </si>
-  <si>
-    <t>2027-02-02 23:59:00</t>
-  </si>
-  <si>
-    <t>美食分享聚餐</t>
-  </si>
-  <si>
-    <t>每個人推薦一道喜歡的料理。</t>
-  </si>
-  <si>
-    <t>2027-03-06 18:30:00</t>
-  </si>
-  <si>
-    <t>2027-03-03 23:59:00</t>
-  </si>
-  <si>
-    <t>主題交流聚會</t>
-  </si>
-  <si>
-    <t>不限主題，自由聊天交流。</t>
-  </si>
-  <si>
-    <t>2027-04-09 14:00:00</t>
-  </si>
-  <si>
-    <t>2027-04-06 23:59:00</t>
-  </si>
-  <si>
-    <t>學習成果分享</t>
-  </si>
-  <si>
-    <t>分享近期學到的新技能。</t>
-  </si>
-  <si>
-    <t>2027-05-15 19:00:00</t>
-  </si>
-  <si>
-    <t>2027-05-12 23:59:00</t>
-  </si>
-  <si>
-    <t>春季小派對</t>
-  </si>
-  <si>
-    <t>簡單聚會，輕音樂聊天。</t>
-  </si>
-  <si>
-    <t>2027-06-04 18:00:00</t>
-  </si>
-  <si>
-    <t>2027-06-01 23:59:00</t>
-  </si>
-  <si>
-    <t>年度自由聚會</t>
-  </si>
-  <si>
-    <t>沒有特定主題的聚會。</t>
-  </si>
-  <si>
-    <t>2027-07-23 19:00:00</t>
-  </si>
-  <si>
-    <t>2027-07-20 23:59:00</t>
-  </si>
-  <si>
-    <t>2025-12-15 9:30:00</t>
-  </si>
-  <si>
-    <t>2026-03-14 13:30:00</t>
-  </si>
-  <si>
-    <t>2026-04-02 10:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-24 8:00:00</t>
-  </si>
-  <si>
-    <t>2026-05-16 7:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-06 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-11 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-01 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-09-03 20:00:00</t>
-  </si>
-  <si>
-    <t>2026-10-09 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-11-14 11:00:00</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
-    <t>2026-12-18 9:00:00</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2025-12-24 11:38:27</t>
-  </si>
-  <si>
-    <t>2025-12-24 11:38:27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星辰縣銀河市星環路 120 號 3 樓（共享空間 A）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市樂音街 45 號 1 樓（音樂咖啡廳）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市學府路 88 號 2 樓 201 室</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市藝文路 160 號（美術館）</t>
-  </si>
-  <si>
-    <t>星辰縣海灣小鎮濱海路 12 號</t>
-  </si>
-  <si>
-    <t>星辰縣河濱鎮河岸路 300 號（河濱公園）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市棋樂街 27 號（桌遊店）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市饗宴路 99 號（美食街）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市天際路 180 號 頂樓（屋頂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市旋律路 52 號 2 樓（音樂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市星航路 10 號 4 樓（會議室 B）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市展星路 200 號（展覽中心）</t>
-  </si>
-  <si>
-    <t>星辰縣山城市雲嶺路 66 號</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市動能路 155 號（運動中心）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市歡聚路 78 號 3 樓（娛樂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市微醺街 33 號（餐酒館）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市晨星路 18 號（咖啡廳）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市學府路 88 號 3 樓 305 室</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市星環路 120 號 5 樓（共享空間 C）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市聚光路 140 號（活動空間）</t>
-  </si>
-  <si>
-    <t>2025-12-16 22:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-14 22:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-11-23 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-11-19 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起分享今年的喜怒哀樂</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -795,7 +797,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1199,57 +1201,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P159"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="I1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -1263,39 +1265,39 @@
         <v>3</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>73</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K2" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="M2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>7</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>8</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1303,13 +1305,13 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2">
         <v>30</v>
@@ -1318,28 +1320,28 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1347,13 +1349,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2">
         <v>50</v>
@@ -1362,30 +1364,30 @@
         <v>5400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1393,13 +1395,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -1408,30 +1410,30 @@
         <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:16" s="11" customFormat="1">
+    <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1439,13 +1441,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
@@ -1454,30 +1456,30 @@
         <v>700</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1485,13 +1487,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2">
         <v>30</v>
@@ -1500,30 +1502,30 @@
         <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1531,13 +1533,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1546,28 +1548,28 @@
         <v>200</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1575,13 +1577,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2">
         <v>15</v>
@@ -1590,30 +1592,30 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:16" s="11" customFormat="1">
+    <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1621,13 +1623,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1636,29 +1638,29 @@
         <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O10" s="9"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1666,13 +1668,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2">
         <v>70</v>
@@ -1681,30 +1683,30 @@
         <v>200</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1712,13 +1714,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2">
         <v>30</v>
@@ -1727,30 +1729,30 @@
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1758,13 +1760,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2">
         <v>60</v>
@@ -1773,30 +1775,30 @@
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1804,13 +1806,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F14" s="2">
         <v>25</v>
@@ -1819,30 +1821,30 @@
         <v>300</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16" s="11" customFormat="1">
+    <row r="15" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1850,13 +1852,13 @@
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F15" s="2">
         <v>15</v>
@@ -1865,30 +1867,30 @@
         <v>200</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1896,13 +1898,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F16" s="2">
         <v>20</v>
@@ -1911,30 +1913,30 @@
         <v>800</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1942,13 +1944,13 @@
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -1957,30 +1959,30 @@
         <v>35000</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1988,13 +1990,13 @@
         <v>24</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F18" s="2">
         <v>18</v>
@@ -2003,30 +2005,30 @@
         <v>500</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2034,13 +2036,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F19" s="2">
         <v>30</v>
@@ -2049,30 +2051,30 @@
         <v>1200</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2080,13 +2082,13 @@
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F20" s="2">
         <v>20</v>
@@ -2095,30 +2097,30 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2126,45 +2128,45 @@
         <v>40</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F21" s="2">
         <v>300</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2172,13 +2174,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -2187,30 +2189,30 @@
         <v>150</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2218,13 +2220,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F23" s="2">
         <v>10</v>
@@ -2233,30 +2235,30 @@
         <v>600</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2264,13 +2266,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F24" s="2">
         <v>28</v>
@@ -2279,30 +2281,30 @@
         <v>400</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2310,13 +2312,13 @@
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F25" s="2">
         <v>14</v>
@@ -2325,30 +2327,30 @@
         <v>250</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2356,13 +2358,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F26" s="2">
         <v>22</v>
@@ -2371,30 +2373,30 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2402,13 +2404,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F27" s="2">
         <v>20</v>
@@ -2417,30 +2419,30 @@
         <v>450</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2448,45 +2450,45 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2494,45 +2496,45 @@
         <v>40</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2">
         <v>3000</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2540,45 +2542,45 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -2586,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F31" s="2">
         <v>16</v>
@@ -2601,30 +2603,30 @@
         <v>200</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -2632,13 +2634,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F32" s="2">
         <v>12</v>
@@ -2647,30 +2649,30 @@
         <v>800</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -2678,13 +2680,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -2693,30 +2695,30 @@
         <v>200</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2724,13 +2726,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F34" s="2">
         <v>20</v>
@@ -2739,30 +2741,30 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -2770,13 +2772,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F35" s="2">
         <v>24</v>
@@ -2785,30 +2787,30 @@
         <v>350</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -2816,13 +2818,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F36" s="2">
         <v>30</v>
@@ -2831,30 +2833,30 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="4"/>
@@ -2872,7 +2874,7 @@
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="4"/>
@@ -2890,7 +2892,7 @@
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="4"/>
@@ -2908,7 +2910,7 @@
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="4"/>
@@ -2926,7 +2928,7 @@
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="4"/>
@@ -2944,7 +2946,7 @@
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="4"/>
@@ -2962,7 +2964,7 @@
       <c r="O42" s="6"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="4"/>
@@ -2980,7 +2982,7 @@
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="4"/>
@@ -2998,7 +3000,7 @@
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3016,7 +3018,7 @@
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3034,7 +3036,7 @@
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3052,7 +3054,7 @@
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3070,7 +3072,7 @@
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3088,7 +3090,7 @@
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3106,7 +3108,7 @@
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3124,7 +3126,7 @@
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3142,7 +3144,7 @@
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3160,7 +3162,7 @@
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3178,7 +3180,7 @@
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3196,7 +3198,7 @@
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3214,7 +3216,7 @@
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3232,7 +3234,7 @@
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3250,7 +3252,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3268,7 +3270,7 @@
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3286,7 +3288,7 @@
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3304,7 +3306,7 @@
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3322,7 +3324,7 @@
       <c r="O62" s="6"/>
       <c r="P62" s="6"/>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3340,7 +3342,7 @@
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3358,7 +3360,7 @@
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3376,7 +3378,7 @@
       <c r="O65" s="6"/>
       <c r="P65" s="6"/>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3394,7 +3396,7 @@
       <c r="O66" s="6"/>
       <c r="P66" s="6"/>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3412,7 +3414,7 @@
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3430,7 +3432,7 @@
       <c r="O68" s="6"/>
       <c r="P68" s="6"/>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3448,7 +3450,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3466,7 +3468,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3484,7 +3486,7 @@
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3502,7 +3504,7 @@
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3520,7 +3522,7 @@
       <c r="O73" s="6"/>
       <c r="P73" s="6"/>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3538,7 +3540,7 @@
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3556,7 +3558,7 @@
       <c r="O75" s="6"/>
       <c r="P75" s="6"/>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3574,7 +3576,7 @@
       <c r="O76" s="6"/>
       <c r="P76" s="6"/>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3592,7 +3594,7 @@
       <c r="O77" s="6"/>
       <c r="P77" s="6"/>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3610,7 +3612,7 @@
       <c r="O78" s="6"/>
       <c r="P78" s="6"/>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3628,7 +3630,7 @@
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3646,7 +3648,7 @@
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3664,7 +3666,7 @@
       <c r="O81" s="6"/>
       <c r="P81" s="6"/>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3682,7 +3684,7 @@
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3700,7 +3702,7 @@
       <c r="O83" s="6"/>
       <c r="P83" s="6"/>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3718,7 +3720,7 @@
       <c r="O84" s="6"/>
       <c r="P84" s="6"/>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3736,7 +3738,7 @@
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3754,7 +3756,7 @@
       <c r="O86" s="6"/>
       <c r="P86" s="6"/>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3772,7 +3774,7 @@
       <c r="O87" s="6"/>
       <c r="P87" s="6"/>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3790,7 +3792,7 @@
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3808,7 +3810,7 @@
       <c r="O89" s="6"/>
       <c r="P89" s="6"/>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3826,7 +3828,7 @@
       <c r="O90" s="6"/>
       <c r="P90" s="6"/>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3844,7 +3846,7 @@
       <c r="O91" s="6"/>
       <c r="P91" s="6"/>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3862,7 +3864,7 @@
       <c r="O92" s="6"/>
       <c r="P92" s="6"/>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3880,7 +3882,7 @@
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="2"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3898,7 +3900,7 @@
       <c r="O94" s="6"/>
       <c r="P94" s="6"/>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3916,7 +3918,7 @@
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3934,7 +3936,7 @@
       <c r="O96" s="6"/>
       <c r="P96" s="6"/>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3952,7 +3954,7 @@
       <c r="O97" s="6"/>
       <c r="P97" s="6"/>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3967,7 +3969,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="2"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3982,7 +3984,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3997,7 +3999,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="2"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4012,7 +4014,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4027,7 +4029,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4042,7 +4044,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4057,7 +4059,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4072,7 +4074,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4087,7 +4089,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4102,7 +4104,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4117,7 +4119,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4132,7 +4134,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4147,7 +4149,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4162,7 +4164,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4177,7 +4179,7 @@
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4192,7 +4194,7 @@
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="2"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4207,7 +4209,7 @@
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="2"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4222,7 +4224,7 @@
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="2"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4237,7 +4239,7 @@
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="2"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4252,7 +4254,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="2"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4267,7 +4269,7 @@
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="2"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4282,7 +4284,7 @@
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4297,7 +4299,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="2"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4312,7 +4314,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="2"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4327,7 +4329,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="2"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4342,7 +4344,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="2"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4357,7 +4359,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="2"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4372,7 +4374,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="2"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4387,7 +4389,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="2"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4402,7 +4404,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4417,7 +4419,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4432,7 +4434,7 @@
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4447,7 +4449,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="2"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4462,7 +4464,7 @@
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="2"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4477,7 +4479,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="2"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4492,7 +4494,7 @@
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="2"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4507,7 +4509,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
@@ -4516,7 +4518,7 @@
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
@@ -4525,7 +4527,7 @@
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
@@ -4534,7 +4536,7 @@
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
@@ -4543,7 +4545,7 @@
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
@@ -4552,7 +4554,7 @@
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
@@ -4561,7 +4563,7 @@
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
@@ -4570,7 +4572,7 @@
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
@@ -4579,7 +4581,7 @@
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -4588,7 +4590,7 @@
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
@@ -4597,77 +4599,77 @@
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
-    <row r="145" spans="10:12">
+    <row r="145" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
     </row>
-    <row r="146" spans="10:12">
+    <row r="146" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="10:12">
+    <row r="147" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="10:12">
+    <row r="148" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="10:12">
+    <row r="149" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="10:12">
+    <row r="150" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="10:12">
+    <row r="151" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="10:12">
+    <row r="152" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="10:12">
+    <row r="153" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="10:12">
+    <row r="154" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="10:12">
+    <row r="155" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="10:12">
+    <row r="156" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="10:12">
+    <row r="157" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="10:12">
+    <row r="158" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="10:12">
+    <row r="159" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>

--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74DD1E-6DC1-4C05-BAE2-2D4DADD3407E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F060805-59ED-4BD6-B099-8147D9DAC27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22830" yWindow="3750" windowWidth="18585" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gathering" sheetId="1" r:id="rId1"/>
@@ -778,15 +778,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dueDate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>活動描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一起分享今年的喜怒哀樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deadline</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>68</v>
@@ -1283,7 +1283,7 @@
         <v>67</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>5</v>
@@ -2499,7 +2499,7 @@
         <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>80</v>

--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F060805-59ED-4BD6-B099-8147D9DAC27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13463B79-AB17-4446-83F7-635400A9A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gathering" sheetId="1" r:id="rId1"/>
@@ -161,12 +161,6 @@
     <t>提供最新知識與技能交流，這是一場AI 開發者社群聚會。</t>
   </si>
   <si>
-    <t>2024-04-19 22:00:00</t>
-  </si>
-  <si>
-    <t>2024-05-06 10:00:00</t>
-  </si>
-  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -787,6 +781,14 @@
   </si>
   <si>
     <t>deadline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-06 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-19 22:00:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1218,16 +1220,16 @@
         <v>9</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>14</v>
@@ -1236,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>17</v>
@@ -1265,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>71</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>4</v>
@@ -1280,10 +1282,10 @@
         <v>16</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>5</v>
@@ -1311,7 +1313,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2">
         <v>30</v>
@@ -1320,25 +1322,25 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -1355,7 +1357,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F4" s="2">
         <v>50</v>
@@ -1364,25 +1366,25 @@
         <v>5400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1401,7 +1403,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -1410,25 +1412,25 @@
         <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -1447,7 +1449,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
@@ -1456,25 +1458,25 @@
         <v>700</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -1493,7 +1495,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="2">
         <v>30</v>
@@ -1502,25 +1504,25 @@
         <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1539,7 +1541,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1548,25 +1550,25 @@
         <v>200</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -1583,7 +1585,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2">
         <v>15</v>
@@ -1592,25 +1594,25 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
@@ -1629,7 +1631,7 @@
         <v>37</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1638,25 +1640,25 @@
         <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O10" s="9"/>
     </row>
@@ -1674,7 +1676,7 @@
         <v>35</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2">
         <v>70</v>
@@ -1683,25 +1685,25 @@
         <v>200</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -1720,7 +1722,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2">
         <v>30</v>
@@ -1729,25 +1731,25 @@
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
@@ -1766,7 +1768,7 @@
         <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2">
         <v>60</v>
@@ -1775,25 +1777,25 @@
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
@@ -1806,13 +1808,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F14" s="2">
         <v>25</v>
@@ -1821,25 +1823,25 @@
         <v>300</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -1852,13 +1854,13 @@
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F15" s="2">
         <v>15</v>
@@ -1867,25 +1869,25 @@
         <v>200</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="L15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
@@ -1898,13 +1900,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F16" s="2">
         <v>20</v>
@@ -1913,25 +1915,25 @@
         <v>800</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
@@ -1950,7 +1952,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -1959,25 +1961,25 @@
         <v>35000</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -1990,13 +1992,13 @@
         <v>24</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F18" s="2">
         <v>18</v>
@@ -2005,25 +2007,25 @@
         <v>500</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -2036,13 +2038,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F19" s="2">
         <v>30</v>
@@ -2051,25 +2053,25 @@
         <v>1200</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -2082,13 +2084,13 @@
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F20" s="2">
         <v>20</v>
@@ -2097,25 +2099,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
@@ -2128,40 +2130,40 @@
         <v>40</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F21" s="2">
         <v>300</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
@@ -2174,13 +2176,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -2189,25 +2191,25 @@
         <v>150</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -2220,13 +2222,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F23" s="2">
         <v>10</v>
@@ -2235,25 +2237,25 @@
         <v>600</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -2266,13 +2268,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F24" s="2">
         <v>28</v>
@@ -2281,25 +2283,25 @@
         <v>400</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
@@ -2312,13 +2314,13 @@
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F25" s="2">
         <v>14</v>
@@ -2327,25 +2329,25 @@
         <v>250</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
@@ -2358,13 +2360,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F26" s="2">
         <v>22</v>
@@ -2373,25 +2375,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
@@ -2404,13 +2406,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F27" s="2">
         <v>20</v>
@@ -2419,25 +2421,25 @@
         <v>450</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
@@ -2450,40 +2452,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
@@ -2496,40 +2498,40 @@
         <v>40</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F29" s="2">
         <v>3000</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
@@ -2542,40 +2544,40 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
@@ -2588,13 +2590,13 @@
         <v>26</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F31" s="2">
         <v>16</v>
@@ -2603,25 +2605,25 @@
         <v>200</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
@@ -2634,13 +2636,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F32" s="2">
         <v>12</v>
@@ -2649,25 +2651,25 @@
         <v>800</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -2680,13 +2682,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -2695,25 +2697,25 @@
         <v>200</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
@@ -2726,13 +2728,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F34" s="2">
         <v>20</v>
@@ -2741,25 +2743,25 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
@@ -2772,13 +2774,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F35" s="2">
         <v>24</v>
@@ -2787,25 +2789,25 @@
         <v>350</v>
       </c>
       <c r="H35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
@@ -2818,13 +2820,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F36" s="2">
         <v>30</v>
@@ -2833,25 +2835,25 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
@@ -4678,5 +4680,8 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G21 G28:G30" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13463B79-AB17-4446-83F7-635400A9A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C61A8E-7293-4E3A-9CB8-589BBB66387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="248">
   <si>
     <t>id</t>
   </si>
@@ -269,10 +269,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025-12-03 10:34:28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-06-01 07:00:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,499 +293,536 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025-12-03 10:40:13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-01 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-05 14:30:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-09 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-19 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-16 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-06 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-24 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-12 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>2025-04-24 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-15 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-22 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-11 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-12 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-09 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-29 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-08 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-14 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-11 00:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-19 12:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-08 11:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-09 16:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-26 17:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-08 19:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-04 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-28 18:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-07-11 05:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-16 23:59:59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOOD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新年交流派對</t>
+  </si>
+  <si>
+    <t>輕鬆聊天迎接新的一年，無主題限制。</t>
+  </si>
+  <si>
+    <t>2026-01-10 18:00:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:59:00</t>
+  </si>
+  <si>
+    <t>音樂分享夜</t>
+  </si>
+  <si>
+    <t>各自帶一首最近喜歡的歌來分享。</t>
+  </si>
+  <si>
+    <t>UPCOMING</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>2026-02-06 19:30:00</t>
+  </si>
+  <si>
+    <t>2026-02-03 23:59:00</t>
+  </si>
+  <si>
+    <t>基礎攝影學習</t>
+  </si>
+  <si>
+    <t>介紹基本構圖概念與實拍練習。</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:59:00</t>
+  </si>
+  <si>
+    <t>春季展覽同行</t>
+  </si>
+  <si>
+    <t>一起看當期藝術展，自由參觀。</t>
+  </si>
+  <si>
+    <t>2026-03-30 23:59:00</t>
+  </si>
+  <si>
+    <t>週末輕旅行</t>
+  </si>
+  <si>
+    <t>一日小旅行，行程不趕。</t>
+  </si>
+  <si>
+    <t>2026-04-18 23:59:00</t>
+  </si>
+  <si>
+    <t>慢跑入門團</t>
+  </si>
+  <si>
+    <t>適合初學者的慢速跑步活動。</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
+  </si>
+  <si>
+    <t>2026-05-13 23:59:00</t>
+  </si>
+  <si>
+    <t>桌遊同樂會</t>
+  </si>
+  <si>
+    <t>以輕策略與派對遊戲為主。</t>
+  </si>
+  <si>
+    <t>GAME</t>
+  </si>
+  <si>
+    <t>2026-06-03 23:59:00</t>
+  </si>
+  <si>
+    <t>美食探店團</t>
+  </si>
+  <si>
+    <t>嘗試新開的餐廳並交流心得。</t>
+  </si>
+  <si>
+    <t>2026-07-08 23:59:00</t>
+  </si>
+  <si>
+    <t>夏日晚間派對</t>
+  </si>
+  <si>
+    <t>簡單音樂與聊天，不吵鬧。</t>
+  </si>
+  <si>
+    <t>2026-07-28 23:59:00</t>
+  </si>
+  <si>
+    <t>歌單交換聚</t>
+  </si>
+  <si>
+    <t>分享彼此的私藏歌單。</t>
+  </si>
+  <si>
+    <t>2026-08-31 23:59:00</t>
+  </si>
+  <si>
+    <t>時間管理學習會</t>
+  </si>
+  <si>
+    <t>分享實用的時間規劃方法。</t>
+  </si>
+  <si>
+    <t>2026-10-06 23:59:00</t>
+  </si>
+  <si>
+    <t>秋季主題展覽</t>
+  </si>
+  <si>
+    <t>參觀設計主題展並交流看法。</t>
+  </si>
+  <si>
+    <t>2026-11-10 23:59:00</t>
+  </si>
+  <si>
+    <t>年度回顧小旅行</t>
+  </si>
+  <si>
+    <t>回顧一年生活的小型旅行。</t>
+  </si>
+  <si>
+    <t>2026-12-12 23:59:00</t>
+  </si>
+  <si>
+    <t>新年運動計畫</t>
+  </si>
+  <si>
+    <t>一起設定 2027 的運動目標。</t>
+  </si>
+  <si>
+    <t>2027-01-08 10:00:00</t>
+  </si>
+  <si>
+    <t>2027-01-05 23:59:00</t>
+  </si>
+  <si>
+    <t>派對遊戲之夜</t>
+  </si>
+  <si>
+    <t>派對型桌遊為主，輕鬆玩。</t>
+  </si>
+  <si>
+    <t>2027-02-05 19:30:00</t>
+  </si>
+  <si>
+    <t>2027-02-02 23:59:00</t>
+  </si>
+  <si>
+    <t>美食分享聚餐</t>
+  </si>
+  <si>
+    <t>每個人推薦一道喜歡的料理。</t>
+  </si>
+  <si>
+    <t>2027-03-06 18:30:00</t>
+  </si>
+  <si>
+    <t>2027-03-03 23:59:00</t>
+  </si>
+  <si>
+    <t>主題交流聚會</t>
+  </si>
+  <si>
+    <t>不限主題，自由聊天交流。</t>
+  </si>
+  <si>
+    <t>2027-04-09 14:00:00</t>
+  </si>
+  <si>
+    <t>2027-04-06 23:59:00</t>
+  </si>
+  <si>
+    <t>學習成果分享</t>
+  </si>
+  <si>
+    <t>分享近期學到的新技能。</t>
+  </si>
+  <si>
+    <t>2027-05-15 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-05-12 23:59:00</t>
+  </si>
+  <si>
+    <t>春季小派對</t>
+  </si>
+  <si>
+    <t>簡單聚會，輕音樂聊天。</t>
+  </si>
+  <si>
+    <t>2027-06-04 18:00:00</t>
+  </si>
+  <si>
+    <t>2027-06-01 23:59:00</t>
+  </si>
+  <si>
+    <t>年度自由聚會</t>
+  </si>
+  <si>
+    <t>沒有特定主題的聚會。</t>
+  </si>
+  <si>
+    <t>2027-07-23 19:00:00</t>
+  </si>
+  <si>
+    <t>2027-07-20 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-03-14 13:30:00</t>
+  </si>
+  <si>
+    <t>2026-04-02 10:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-24 8:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-16 7:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-06 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-11 12:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-01 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-09 19:00:00</t>
+  </si>
+  <si>
+    <t>2026-11-14 11:00:00</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>2026-12-18 9:00:00</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 3 樓（共享空間 A）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市樂音街 45 號 1 樓（音樂咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 2 樓 201 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市藝文路 160 號（美術館）</t>
+  </si>
+  <si>
+    <t>星辰縣海灣小鎮濱海路 12 號</t>
+  </si>
+  <si>
+    <t>星辰縣河濱鎮河岸路 300 號（河濱公園）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市棋樂街 27 號（桌遊店）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市饗宴路 99 號（美食街）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市天際路 180 號 頂樓（屋頂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市旋律路 52 號 2 樓（音樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星航路 10 號 4 樓（會議室 B）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市展星路 200 號（展覽中心）</t>
+  </si>
+  <si>
+    <t>星辰縣山城市雲嶺路 66 號</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市動能路 155 號（運動中心）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市歡聚路 78 號 3 樓（娛樂空間）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市微醺街 33 號（餐酒館）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市晨星路 18 號（咖啡廳）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市學府路 88 號 3 樓 305 室</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市星環路 120 號 5 樓（共享空間 C）</t>
+  </si>
+  <si>
+    <t>星辰縣銀河市聚光路 140 號（活動空間）</t>
+  </si>
+  <si>
+    <t>2025-12-16 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-12-14 22:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-23 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-19 10:00:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起分享今年的喜怒哀樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deadline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-05 12:00:00</t>
+  </si>
+  <si>
+    <t>2025-01-25 11:00:00</t>
+  </si>
+  <si>
+    <t>2025-02-23 16:00:00</t>
+  </si>
+  <si>
+    <t>2025-02-25 00:00:00</t>
+  </si>
+  <si>
+    <t>2025-03-12 17:00:00</t>
+  </si>
+  <si>
+    <t>2025-03-25 19:00:00</t>
+  </si>
+  <si>
+    <t>2025-03-31 11:00:00</t>
   </si>
   <si>
     <t>2025-04-14 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-24 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-15 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-22 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-11 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-12 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-09 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-09 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-29 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-05-08 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-14 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-11 00:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-01-19 12:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-02-08 11:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-09 16:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-03-26 17:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-08 19:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-05-04 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-28 18:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-01 13:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-07-11 05:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-03-16 23:59:59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FOOD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新年交流派對</t>
-  </si>
-  <si>
-    <t>輕鬆聊天迎接新的一年，無主題限制。</t>
-  </si>
-  <si>
-    <t>2026-01-10 18:00:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 23:59:00</t>
-  </si>
-  <si>
-    <t>2025-12-01 10:00:00</t>
-  </si>
-  <si>
-    <t>音樂分享夜</t>
-  </si>
-  <si>
-    <t>各自帶一首最近喜歡的歌來分享。</t>
-  </si>
-  <si>
-    <t>UPCOMING</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>2026-02-06 19:30:00</t>
-  </si>
-  <si>
-    <t>2026-02-03 23:59:00</t>
-  </si>
-  <si>
-    <t>基礎攝影學習</t>
-  </si>
-  <si>
-    <t>介紹基本構圖概念與實拍練習。</t>
-  </si>
-  <si>
-    <t>2026-03-10 23:59:00</t>
-  </si>
-  <si>
-    <t>春季展覽同行</t>
-  </si>
-  <si>
-    <t>一起看當期藝術展，自由參觀。</t>
-  </si>
-  <si>
-    <t>2026-03-30 23:59:00</t>
-  </si>
-  <si>
-    <t>週末輕旅行</t>
-  </si>
-  <si>
-    <t>一日小旅行，行程不趕。</t>
-  </si>
-  <si>
-    <t>2026-04-18 23:59:00</t>
-  </si>
-  <si>
-    <t>慢跑入門團</t>
-  </si>
-  <si>
-    <t>適合初學者的慢速跑步活動。</t>
-  </si>
-  <si>
-    <t>SPORTS</t>
-  </si>
-  <si>
-    <t>2026-05-13 23:59:00</t>
-  </si>
-  <si>
-    <t>桌遊同樂會</t>
-  </si>
-  <si>
-    <t>以輕策略與派對遊戲為主。</t>
-  </si>
-  <si>
-    <t>GAME</t>
-  </si>
-  <si>
-    <t>2026-06-03 23:59:00</t>
-  </si>
-  <si>
-    <t>美食探店團</t>
-  </si>
-  <si>
-    <t>嘗試新開的餐廳並交流心得。</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:59:00</t>
-  </si>
-  <si>
-    <t>夏日晚間派對</t>
-  </si>
-  <si>
-    <t>簡單音樂與聊天，不吵鬧。</t>
-  </si>
-  <si>
-    <t>2026-07-28 23:59:00</t>
-  </si>
-  <si>
-    <t>歌單交換聚</t>
-  </si>
-  <si>
-    <t>分享彼此的私藏歌單。</t>
-  </si>
-  <si>
-    <t>2026-08-31 23:59:00</t>
-  </si>
-  <si>
-    <t>時間管理學習會</t>
-  </si>
-  <si>
-    <t>分享實用的時間規劃方法。</t>
-  </si>
-  <si>
-    <t>2026-10-06 23:59:00</t>
-  </si>
-  <si>
-    <t>秋季主題展覽</t>
-  </si>
-  <si>
-    <t>參觀設計主題展並交流看法。</t>
-  </si>
-  <si>
-    <t>2026-11-10 23:59:00</t>
-  </si>
-  <si>
-    <t>年度回顧小旅行</t>
-  </si>
-  <si>
-    <t>回顧一年生活的小型旅行。</t>
-  </si>
-  <si>
-    <t>2026-12-12 23:59:00</t>
-  </si>
-  <si>
-    <t>新年運動計畫</t>
-  </si>
-  <si>
-    <t>一起設定 2027 的運動目標。</t>
-  </si>
-  <si>
-    <t>2027-01-08 10:00:00</t>
-  </si>
-  <si>
-    <t>2027-01-05 23:59:00</t>
-  </si>
-  <si>
-    <t>派對遊戲之夜</t>
-  </si>
-  <si>
-    <t>派對型桌遊為主，輕鬆玩。</t>
-  </si>
-  <si>
-    <t>2027-02-05 19:30:00</t>
-  </si>
-  <si>
-    <t>2027-02-02 23:59:00</t>
-  </si>
-  <si>
-    <t>美食分享聚餐</t>
-  </si>
-  <si>
-    <t>每個人推薦一道喜歡的料理。</t>
-  </si>
-  <si>
-    <t>2027-03-06 18:30:00</t>
-  </si>
-  <si>
-    <t>2027-03-03 23:59:00</t>
-  </si>
-  <si>
-    <t>主題交流聚會</t>
-  </si>
-  <si>
-    <t>不限主題，自由聊天交流。</t>
-  </si>
-  <si>
-    <t>2027-04-09 14:00:00</t>
-  </si>
-  <si>
-    <t>2027-04-06 23:59:00</t>
-  </si>
-  <si>
-    <t>學習成果分享</t>
-  </si>
-  <si>
-    <t>分享近期學到的新技能。</t>
-  </si>
-  <si>
-    <t>2027-05-15 19:00:00</t>
-  </si>
-  <si>
-    <t>2027-05-12 23:59:00</t>
-  </si>
-  <si>
-    <t>春季小派對</t>
-  </si>
-  <si>
-    <t>簡單聚會，輕音樂聊天。</t>
-  </si>
-  <si>
-    <t>2027-06-04 18:00:00</t>
-  </si>
-  <si>
-    <t>2027-06-01 23:59:00</t>
-  </si>
-  <si>
-    <t>年度自由聚會</t>
-  </si>
-  <si>
-    <t>沒有特定主題的聚會。</t>
-  </si>
-  <si>
-    <t>2027-07-23 19:00:00</t>
-  </si>
-  <si>
-    <t>2027-07-20 23:59:00</t>
-  </si>
-  <si>
-    <t>2025-12-15 9:30:00</t>
-  </si>
-  <si>
-    <t>2026-03-14 13:30:00</t>
-  </si>
-  <si>
-    <t>2026-04-02 10:00:00</t>
-  </si>
-  <si>
-    <t>2026-04-24 8:00:00</t>
-  </si>
-  <si>
-    <t>2026-05-16 7:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-06 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-11 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-01 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-09-03 20:00:00</t>
-  </si>
-  <si>
-    <t>2026-10-09 19:00:00</t>
-  </si>
-  <si>
-    <t>2026-11-14 11:00:00</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
-    <t>2026-12-18 9:00:00</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2025-12-24 11:38:27</t>
-  </si>
-  <si>
-    <t>2025-12-24 11:38:27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星辰縣銀河市星環路 120 號 3 樓（共享空間 A）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市樂音街 45 號 1 樓（音樂咖啡廳）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市學府路 88 號 2 樓 201 室</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市藝文路 160 號（美術館）</t>
-  </si>
-  <si>
-    <t>星辰縣海灣小鎮濱海路 12 號</t>
-  </si>
-  <si>
-    <t>星辰縣河濱鎮河岸路 300 號（河濱公園）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市棋樂街 27 號（桌遊店）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市饗宴路 99 號（美食街）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市天際路 180 號 頂樓（屋頂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市旋律路 52 號 2 樓（音樂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市星航路 10 號 4 樓（會議室 B）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市展星路 200 號（展覽中心）</t>
-  </si>
-  <si>
-    <t>星辰縣山城市雲嶺路 66 號</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市動能路 155 號（運動中心）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市歡聚路 78 號 3 樓（娛樂空間）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市微醺街 33 號（餐酒館）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市晨星路 18 號（咖啡廳）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市學府路 88 號 3 樓 305 室</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市星環路 120 號 5 樓（共享空間 C）</t>
-  </si>
-  <si>
-    <t>星辰縣銀河市聚光路 140 號（活動空間）</t>
-  </si>
-  <si>
-    <t>2025-12-16 22:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-12-14 22:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-11-23 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-11-19 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一起分享今年的喜怒哀樂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deadline</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-05-06 10:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-04-19 22:00:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-20 18:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-05 10:00:00</t>
+  </si>
+  <si>
+    <t>2025-11-30 22:00:00</t>
+  </si>
+  <si>
+    <t>2025-12-24 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-01-20 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 23:59:59</t>
+  </si>
+  <si>
+    <t>2026-03-16 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-04-04 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-04-29 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-05-11 23:59:59</t>
+  </si>
+  <si>
+    <t>2026-05-20 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-06-24 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-07-14 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-08-17 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-09-22 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-10-27 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-11-28 23:59:00</t>
+  </si>
+  <si>
+    <t>2026-12-12 23:59:59</t>
+  </si>
+  <si>
+    <t>2026-12-22 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-01-19 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-02-17 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-03-23 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-04-28 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-05-18 23:59:00</t>
+  </si>
+  <si>
+    <t>2027-07-06 23:59:00</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>66</v>
@@ -1285,7 +1318,7 @@
         <v>65</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>5</v>
@@ -1325,22 +1358,22 @@
         <v>43</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -1372,19 +1405,19 @@
         <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>85</v>
+        <v>215</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>85</v>
+        <v>215</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
@@ -1418,19 +1451,19 @@
         <v>44</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
@@ -1464,19 +1497,19 @@
         <v>47</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -1510,19 +1543,19 @@
         <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
@@ -1556,19 +1589,19 @@
         <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -1600,19 +1633,19 @@
         <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
@@ -1646,19 +1679,19 @@
         <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>90</v>
+        <v>221</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>90</v>
+        <v>221</v>
       </c>
       <c r="O10" s="9"/>
     </row>
@@ -1691,19 +1724,19 @@
         <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -1731,25 +1764,25 @@
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
@@ -1777,25 +1810,25 @@
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>49</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
@@ -1808,13 +1841,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F14" s="2">
         <v>25</v>
@@ -1829,19 +1862,19 @@
         <v>44</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -1854,13 +1887,13 @@
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F15" s="2">
         <v>15</v>
@@ -1872,22 +1905,22 @@
         <v>42</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
@@ -1900,13 +1933,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F16" s="2">
         <v>20</v>
@@ -1921,19 +1954,19 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
@@ -1967,19 +2000,19 @@
         <v>46</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -1992,13 +2025,13 @@
         <v>24</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="F18" s="2">
         <v>18</v>
@@ -2013,19 +2046,19 @@
         <v>47</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="L18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -2038,13 +2071,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="F19" s="2">
         <v>30</v>
@@ -2059,19 +2092,19 @@
         <v>46</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -2084,13 +2117,13 @@
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="F20" s="2">
         <v>20</v>
@@ -2102,22 +2135,22 @@
         <v>42</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
@@ -2151,19 +2184,19 @@
         <v>44</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>74</v>
+        <v>232</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>74</v>
+        <v>232</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
@@ -2176,13 +2209,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -2194,22 +2227,22 @@
         <v>42</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -2222,13 +2255,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F23" s="2">
         <v>10</v>
@@ -2243,19 +2276,19 @@
         <v>48</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -2268,13 +2301,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F24" s="2">
         <v>28</v>
@@ -2289,19 +2322,19 @@
         <v>44</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
@@ -2314,13 +2347,13 @@
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F25" s="2">
         <v>14</v>
@@ -2332,22 +2365,22 @@
         <v>42</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
@@ -2360,13 +2393,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F26" s="2">
         <v>22</v>
@@ -2381,19 +2414,19 @@
         <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="L26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
@@ -2406,13 +2439,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F27" s="2">
         <v>20</v>
@@ -2427,19 +2460,19 @@
         <v>47</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
@@ -2452,19 +2485,19 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>42</v>
@@ -2473,19 +2506,19 @@
         <v>46</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
@@ -2498,13 +2531,13 @@
         <v>40</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="F29" s="2">
         <v>3000</v>
@@ -2519,19 +2552,19 @@
         <v>44</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
@@ -2544,40 +2577,40 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
@@ -2590,13 +2623,13 @@
         <v>26</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="F31" s="2">
         <v>16</v>
@@ -2608,22 +2641,22 @@
         <v>42</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
@@ -2636,13 +2669,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F32" s="2">
         <v>12</v>
@@ -2657,19 +2690,19 @@
         <v>48</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -2682,13 +2715,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -2703,19 +2736,19 @@
         <v>49</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
@@ -2728,13 +2761,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F34" s="2">
         <v>20</v>
@@ -2749,19 +2782,19 @@
         <v>45</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="L34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
@@ -2774,13 +2807,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F35" s="2">
         <v>24</v>
@@ -2795,19 +2828,19 @@
         <v>44</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
@@ -2820,13 +2853,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F36" s="2">
         <v>30</v>
@@ -2841,19 +2874,19 @@
         <v>49</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>

--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C61A8E-7293-4E3A-9CB8-589BBB66387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C0A8D6-78CF-4434-A2D0-FAC5D50C7F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="246">
   <si>
     <t>id</t>
   </si>
@@ -164,9 +164,6 @@
     <t>OPEN</t>
   </si>
   <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
     <t>PARTY</t>
   </si>
   <si>
@@ -393,9 +390,6 @@
   </si>
   <si>
     <t>各自帶一首最近喜歡的歌來分享。</t>
-  </si>
-  <si>
-    <t>UPCOMING</t>
   </si>
   <si>
     <t>MUSIC</t>
@@ -832,7 +826,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,15 +863,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -912,7 +897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -935,9 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1235,104 +1217,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P159"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1346,7 +1326,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2">
         <v>30</v>
@@ -1355,28 +1335,28 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1390,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2">
         <v>50</v>
@@ -1399,30 +1379,28 @@
         <v>5400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1436,7 +1414,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -1445,30 +1423,28 @@
         <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1482,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="2">
         <v>30</v>
@@ -1491,30 +1467,28 @@
         <v>700</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1528,7 +1502,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2">
         <v>30</v>
@@ -1537,30 +1511,28 @@
         <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1574,7 +1546,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2">
         <v>30</v>
@@ -1583,28 +1555,28 @@
         <v>200</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1618,7 +1590,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2">
         <v>15</v>
@@ -1627,30 +1599,28 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1664,7 +1634,7 @@
         <v>37</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2">
         <v>30</v>
@@ -1673,29 +1643,28 @@
         <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="O10" s="9"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1709,7 +1678,7 @@
         <v>35</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2">
         <v>70</v>
@@ -1718,30 +1687,28 @@
         <v>200</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1755,7 +1722,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2">
         <v>30</v>
@@ -1764,30 +1731,28 @@
         <v>200</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1801,7 +1766,7 @@
         <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2">
         <v>60</v>
@@ -1810,30 +1775,28 @@
         <v>200</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1841,13 +1804,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F14" s="2">
         <v>25</v>
@@ -1859,27 +1822,25 @@
         <v>42</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="L14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1887,13 +1848,13 @@
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F15" s="2">
         <v>15</v>
@@ -1905,27 +1866,25 @@
         <v>42</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="L15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1933,13 +1892,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2">
         <v>20</v>
@@ -1951,27 +1910,25 @@
         <v>42</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1985,7 +1942,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -1997,27 +1954,25 @@
         <v>42</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="L17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2025,13 +1980,13 @@
         <v>24</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F18" s="2">
         <v>18</v>
@@ -2043,27 +1998,25 @@
         <v>42</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2071,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F19" s="2">
         <v>30</v>
@@ -2089,27 +2042,25 @@
         <v>42</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2117,13 +2068,13 @@
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F20" s="2">
         <v>20</v>
@@ -2135,27 +2086,25 @@
         <v>42</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2163,45 +2112,43 @@
         <v>40</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="F21" s="2">
         <v>300</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="L21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2209,13 +2156,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F22" s="2">
         <v>12</v>
@@ -2227,27 +2174,25 @@
         <v>42</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2255,13 +2200,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F23" s="2">
         <v>10</v>
@@ -2273,27 +2218,25 @@
         <v>42</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2301,13 +2244,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F24" s="2">
         <v>28</v>
@@ -2319,27 +2262,25 @@
         <v>42</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2347,13 +2288,13 @@
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F25" s="2">
         <v>14</v>
@@ -2365,27 +2306,25 @@
         <v>42</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2393,13 +2332,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F26" s="2">
         <v>22</v>
@@ -2411,27 +2350,25 @@
         <v>42</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2439,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F27" s="2">
         <v>20</v>
@@ -2457,27 +2394,25 @@
         <v>42</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2485,45 +2420,43 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F28" s="2">
         <v>16</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2531,45 +2464,43 @@
         <v>40</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="F29" s="2">
         <v>3000</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2577,45 +2508,43 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2">
         <v>18</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -2623,13 +2552,13 @@
         <v>26</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F31" s="2">
         <v>16</v>
@@ -2641,27 +2570,25 @@
         <v>42</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -2669,13 +2596,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F32" s="2">
         <v>12</v>
@@ -2687,27 +2614,25 @@
         <v>42</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -2715,13 +2640,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
@@ -2733,27 +2658,25 @@
         <v>42</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2761,13 +2684,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F34" s="2">
         <v>20</v>
@@ -2779,27 +2702,25 @@
         <v>42</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -2807,13 +2728,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F35" s="2">
         <v>24</v>
@@ -2825,27 +2746,25 @@
         <v>42</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -2853,13 +2772,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F36" s="2">
         <v>30</v>
@@ -2871,27 +2790,25 @@
         <v>42</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="4"/>
@@ -2906,10 +2823,8 @@
       <c r="L37" s="2"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="4"/>
@@ -2924,10 +2839,8 @@
       <c r="L38" s="2"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="4"/>
@@ -2942,10 +2855,8 @@
       <c r="L39" s="2"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="4"/>
@@ -2960,10 +2871,8 @@
       <c r="L40" s="2"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="4"/>
@@ -2978,10 +2887,8 @@
       <c r="L41" s="2"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="4"/>
@@ -2996,10 +2903,8 @@
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="4"/>
@@ -3014,10 +2919,8 @@
       <c r="L43" s="2"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="4"/>
@@ -3032,10 +2935,8 @@
       <c r="L44" s="2"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3050,10 +2951,8 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3068,10 +2967,8 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3086,10 +2983,8 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3104,10 +2999,8 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3122,10 +3015,8 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3140,10 +3031,8 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3158,10 +3047,8 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3176,10 +3063,8 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3194,10 +3079,8 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3212,10 +3095,8 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3230,10 +3111,8 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3248,10 +3127,8 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3266,10 +3143,8 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3284,10 +3159,8 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3302,10 +3175,8 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3320,10 +3191,8 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3338,10 +3207,8 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3356,10 +3223,8 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3374,10 +3239,8 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3392,10 +3255,8 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="6"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3410,10 +3271,8 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3428,10 +3287,8 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3446,10 +3303,8 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="6"/>
-      <c r="O67" s="6"/>
-      <c r="P67" s="6"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3464,10 +3319,8 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="6"/>
-      <c r="O68" s="6"/>
-      <c r="P68" s="6"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3482,10 +3335,8 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3500,10 +3351,8 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3518,10 +3367,8 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="6"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3536,10 +3383,8 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3554,10 +3399,8 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3572,10 +3415,8 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
-      <c r="P74" s="6"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3590,10 +3431,8 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3608,10 +3447,8 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="6"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3626,10 +3463,8 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="6"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3644,10 +3479,8 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
-      <c r="P78" s="6"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3662,10 +3495,8 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
-      <c r="P79" s="6"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3680,10 +3511,8 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3698,10 +3527,8 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="6"/>
-      <c r="O81" s="6"/>
-      <c r="P81" s="6"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3716,10 +3543,8 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="6"/>
-      <c r="O82" s="6"/>
-      <c r="P82" s="6"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3734,10 +3559,8 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="6"/>
-      <c r="O83" s="6"/>
-      <c r="P83" s="6"/>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3752,10 +3575,8 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="6"/>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3770,10 +3591,8 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="6"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="2"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3788,10 +3607,8 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="6"/>
-      <c r="O86" s="6"/>
-      <c r="P86" s="6"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3806,10 +3623,8 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="6"/>
-      <c r="O87" s="6"/>
-      <c r="P87" s="6"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3824,10 +3639,8 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="6"/>
-      <c r="O88" s="6"/>
-      <c r="P88" s="6"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3842,10 +3655,8 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="6"/>
-      <c r="O89" s="6"/>
-      <c r="P89" s="6"/>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3860,10 +3671,8 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="6"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3878,10 +3687,8 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="6"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3896,10 +3703,8 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
       <c r="N92" s="6"/>
-      <c r="O92" s="6"/>
-      <c r="P92" s="6"/>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3914,10 +3719,8 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
       <c r="N93" s="6"/>
-      <c r="O93" s="6"/>
-      <c r="P93" s="6"/>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3932,10 +3735,8 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="6"/>
-      <c r="O94" s="6"/>
-      <c r="P94" s="6"/>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3950,10 +3751,8 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="6"/>
-      <c r="O95" s="6"/>
-      <c r="P95" s="6"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3968,10 +3767,8 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
       <c r="N96" s="6"/>
-      <c r="O96" s="6"/>
-      <c r="P96" s="6"/>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3986,10 +3783,8 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
       <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4004,7 +3799,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4019,7 +3814,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4034,7 +3829,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="2"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4049,7 +3844,7 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4064,7 +3859,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4079,7 +3874,7 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4094,7 +3889,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4109,7 +3904,7 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4124,7 +3919,7 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4139,7 +3934,7 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4154,7 +3949,7 @@
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4169,7 +3964,7 @@
       <c r="L109" s="3"/>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4184,7 +3979,7 @@
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4199,7 +3994,7 @@
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4549,7 +4344,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
       <c r="I135" s="8"/>
-      <c r="J135" s="10"/>
+      <c r="J135" s="9"/>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
@@ -4558,7 +4353,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
       <c r="I136" s="8"/>
-      <c r="J136" s="10"/>
+      <c r="J136" s="9"/>
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
@@ -4567,7 +4362,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
       <c r="I137" s="8"/>
-      <c r="J137" s="10"/>
+      <c r="J137" s="9"/>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
@@ -4576,7 +4371,7 @@
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
       <c r="I138" s="8"/>
-      <c r="J138" s="10"/>
+      <c r="J138" s="9"/>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
@@ -4585,7 +4380,7 @@
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
       <c r="I139" s="8"/>
-      <c r="J139" s="10"/>
+      <c r="J139" s="9"/>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
@@ -4594,7 +4389,7 @@
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
       <c r="I140" s="8"/>
-      <c r="J140" s="10"/>
+      <c r="J140" s="9"/>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
@@ -4603,7 +4398,7 @@
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
       <c r="I141" s="8"/>
-      <c r="J141" s="10"/>
+      <c r="J141" s="9"/>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
@@ -4612,7 +4407,7 @@
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
       <c r="I142" s="8"/>
-      <c r="J142" s="10"/>
+      <c r="J142" s="9"/>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
@@ -4621,7 +4416,7 @@
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
       <c r="I143" s="8"/>
-      <c r="J143" s="10"/>
+      <c r="J143" s="9"/>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
@@ -4630,7 +4425,7 @@
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
       <c r="I144" s="8"/>
-      <c r="J144" s="10"/>
+      <c r="J144" s="9"/>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>

--- a/data/Gathering.xlsx
+++ b/data/Gathering.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\Gathering_Island\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\gathering-island-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C56607-38C6-4B32-87B1-88F2E61D8710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA60817-4610-4A58-9237-DFED95D043C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3852,7 +3852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3877,9 +3877,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4170,7 +4167,7 @@
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="12" width="28.625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="28.625" style="12" customWidth="1"/>
+    <col min="13" max="14" width="28.625" style="11" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4211,10 +4208,10 @@
       <c r="L1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4297,7 +4294,7 @@
         <v>547</v>
       </c>
       <c r="L3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>548</v>
@@ -4957,7 +4954,7 @@
         <v>88</v>
       </c>
       <c r="L18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>218</v>
@@ -5353,7 +5350,7 @@
         <v>589</v>
       </c>
       <c r="L27" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>590</v>
@@ -6145,7 +6142,7 @@
         <v>997</v>
       </c>
       <c r="L45" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>998</v>
@@ -6673,7 +6670,7 @@
         <v>914</v>
       </c>
       <c r="L57" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>720</v>
@@ -7025,7 +7022,7 @@
         <v>628</v>
       </c>
       <c r="L65" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="3" t="s">
         <v>455</v>
@@ -7597,7 +7594,7 @@
         <v>330</v>
       </c>
       <c r="L78" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>253</v>
@@ -7801,7 +7798,7 @@
       <c r="F83" s="2">
         <v>14</v>
       </c>
-      <c r="G83" s="10">
+      <c r="G83" s="5">
         <v>400</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -7845,7 +7842,7 @@
       <c r="F84" s="2">
         <v>18</v>
       </c>
-      <c r="G84" s="10">
+      <c r="G84" s="5">
         <v>300</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -8257,7 +8254,7 @@
         <v>361</v>
       </c>
       <c r="L93" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="3" t="s">
         <v>305</v>
@@ -8785,7 +8782,7 @@
         <v>359</v>
       </c>
       <c r="L105" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="3" t="s">
         <v>638</v>
@@ -9577,7 +9574,7 @@
         <v>1055</v>
       </c>
       <c r="L123" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="3" t="s">
         <v>648</v>
@@ -10369,7 +10366,7 @@
         <v>772</v>
       </c>
       <c r="L141" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="3" t="s">
         <v>773</v>
@@ -11161,7 +11158,7 @@
         <v>494</v>
       </c>
       <c r="L159" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="3" t="s">
         <v>495</v>
@@ -11953,7 +11950,7 @@
         <v>506</v>
       </c>
       <c r="L177" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" s="3" t="s">
         <v>507</v>
@@ -12745,7 +12742,7 @@
         <v>167</v>
       </c>
       <c r="L195" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" s="3" t="s">
         <v>244</v>
@@ -13405,7 +13402,7 @@
         <v>890</v>
       </c>
       <c r="L210" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" s="3" t="s">
         <v>860</v>
@@ -13493,7 +13490,7 @@
         <v>541</v>
       </c>
       <c r="L212" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M212" s="3" t="s">
         <v>542</v>
@@ -13625,7 +13622,7 @@
         <v>904</v>
       </c>
       <c r="L215" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M215" s="3" t="s">
         <v>865</v>
